--- a/data/trans_orig/LAWTONB_2R3-Edad-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R3-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11351</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29886</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23694</t>
+          <t>24514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45999</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39675</t>
+          <t>39099</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68272</t>
+          <t>66253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262697</t>
+          <t>262821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280613</t>
+          <t>281232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>296935</t>
+          <t>297262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>319240</t>
+          <t>318420</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567245</t>
+          <t>569264</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>595842</t>
+          <t>596418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35479</t>
+          <t>35404</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57825</t>
+          <t>58257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74257</t>
+          <t>75115</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108507</t>
+          <t>108695</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>118147</t>
+          <t>118569</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159566</t>
+          <t>160326</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>152058</t>
+          <t>151626</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174404</t>
+          <t>174479</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>225401</t>
+          <t>225213</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>259651</t>
+          <t>258793</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>384225</t>
+          <t>383465</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>425644</t>
+          <t>425222</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,2%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51284</t>
+          <t>52804</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80384</t>
+          <t>81300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>105642</t>
+          <t>105823</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146624</t>
+          <t>147711</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164711</t>
+          <t>164992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216682</t>
+          <t>215710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>422082</t>
+          <t>421166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>451182</t>
+          <t>449662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530218</t>
+          <t>529131</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>571200</t>
+          <t>571019</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>962626</t>
+          <t>963598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1014597</t>
+          <t>1014316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>20087</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41075</t>
+          <t>43409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>28464</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52668</t>
+          <t>55003</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55031</t>
+          <t>54874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87790</t>
+          <t>90031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>268711</t>
+          <t>266377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>289180</t>
+          <t>289699</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301328</t>
+          <t>298993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>325110</t>
+          <t>325532</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>575992</t>
+          <t>573751</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>608751</t>
+          <t>608908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69987</t>
+          <t>70986</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102909</t>
+          <t>104754</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137363</t>
+          <t>136110</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176012</t>
+          <t>175373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>215914</t>
+          <t>215952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>266743</t>
+          <t>268072</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,96%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146942</t>
+          <t>145097</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179864</t>
+          <t>178865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,81%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>212967</t>
+          <t>213606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251616</t>
+          <t>252869</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>372087</t>
+          <t>370758</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422916</t>
+          <t>422878</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97438</t>
+          <t>95353</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137651</t>
+          <t>138893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172810</t>
+          <t>171588</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>223623</t>
+          <t>219962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>278494</t>
+          <t>281438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>343070</t>
+          <t>342188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,27%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>421986</t>
+          <t>420744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>462199</t>
+          <t>464284</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>519352</t>
+          <t>523013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>570165</t>
+          <t>571387</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>959542</t>
+          <t>960424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1024118</t>
+          <t>1021174</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13365</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>32550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25576</t>
+          <t>25297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49513</t>
+          <t>47381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44451</t>
+          <t>44281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74105</t>
+          <t>74432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303102</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>320965</t>
+          <t>320757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>328249</t>
+          <t>330381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>352186</t>
+          <t>352465</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>637987</t>
+          <t>637660</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>667641</t>
+          <t>667811</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55832</t>
+          <t>54527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81432</t>
+          <t>80550</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>126897</t>
+          <t>125106</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>172869</t>
+          <t>169034</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>190676</t>
+          <t>190724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>242129</t>
+          <t>243362</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,03%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175566</t>
+          <t>176448</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>201166</t>
+          <t>202471</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>227300</t>
+          <t>231135</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>273272</t>
+          <t>275063</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415038</t>
+          <t>413805</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>466491</t>
+          <t>466443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,98%</t>
         </is>
       </c>
     </row>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>72292</t>
+          <t>74075</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106074</t>
+          <t>106225</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>160121</t>
+          <t>157849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>212250</t>
+          <t>210046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242771</t>
+          <t>241978</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>306347</t>
+          <t>303179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485254</t>
+          <t>485103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519036</t>
+          <t>517253</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>565681</t>
+          <t>567885</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>617810</t>
+          <t>620082</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1062912</t>
+          <t>1066080</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1126488</t>
+          <t>1127281</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -4505,32 +4505,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>26455</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19701</t>
+          <t>21066</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>34644</t>
+          <t>37211</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39073</t>
+          <t>43930</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>35657</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>62495</t>
+          <t>53788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4575,32 +4575,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>65528</t>
+          <t>72052</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>58744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88908</t>
+          <t>85173</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -4618,32 +4618,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>338001</t>
+          <t>375018</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>329812</t>
+          <t>365929</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>344755</t>
+          <t>382074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4653,32 +4653,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>567515</t>
+          <t>393390</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>544093</t>
+          <t>383532</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>589770</t>
+          <t>401663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4688,32 +4688,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>905517</t>
+          <t>768408</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882137</t>
+          <t>755287</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>936989</t>
+          <t>781716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -4731,17 +4731,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>364456</t>
+          <t>403140</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>364456</t>
+          <t>403140</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>364456</t>
+          <t>403140</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4766,17 +4766,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>606588</t>
+          <t>437320</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>606588</t>
+          <t>437320</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>606588</t>
+          <t>437320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4801,17 +4801,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>971045</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>971045</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>971045</t>
+          <t>840460</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>80176</t>
+          <t>85417</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68659</t>
+          <t>73158</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93001</t>
+          <t>97871</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>195003</t>
+          <t>211452</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>181293</t>
+          <t>196486</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>209228</t>
+          <t>227245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4918,32 +4918,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>275179</t>
+          <t>296868</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>255962</t>
+          <t>278285</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>294002</t>
+          <t>318391</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -4961,32 +4961,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>199772</t>
+          <t>221650</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186947</t>
+          <t>209196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211289</t>
+          <t>233909</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>227632</t>
+          <t>249446</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>213407</t>
+          <t>233653</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>241342</t>
+          <t>264412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5031,32 +5031,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>427404</t>
+          <t>471096</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>408581</t>
+          <t>449573</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>446621</t>
+          <t>489679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,76%</t>
         </is>
       </c>
     </row>
@@ -5074,17 +5074,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>279948</t>
+          <t>307067</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>422635</t>
+          <t>460898</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>422635</t>
+          <t>460898</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>422635</t>
+          <t>460898</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5144,17 +5144,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>702583</t>
+          <t>767964</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>702583</t>
+          <t>767964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>702583</t>
+          <t>767964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>106631</t>
+          <t>113539</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92603</t>
+          <t>97888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>123621</t>
+          <t>130066</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>234077</t>
+          <t>255382</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>123513</t>
+          <t>236056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>300052</t>
+          <t>274210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>340708</t>
+          <t>368920</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>229064</t>
+          <t>344204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>399571</t>
+          <t>396063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -5304,32 +5304,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>537773</t>
+          <t>596668</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>520783</t>
+          <t>580141</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>551801</t>
+          <t>612319</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>795147</t>
+          <t>642836</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>729172</t>
+          <t>624008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>905711</t>
+          <t>662162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5374,32 +5374,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1332920</t>
+          <t>1239504</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1274057</t>
+          <t>1212361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1444564</t>
+          <t>1264220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>78,6%</t>
         </is>
       </c>
     </row>
@@ -5417,17 +5417,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5487,17 +5487,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
